--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104416254</v>
+        <v>104416256</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vångaberget, östsluttning, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461463.9487752133</v>
+        <v>461496</v>
       </c>
       <c r="R2" t="n">
-        <v>6223113.853939298</v>
+        <v>6223060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +746,18 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,53 +776,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104416255</v>
+        <v>107657751</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vångaberget, östsluttning, Sk</t>
+          <t>Vånga, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461430.7146287801</v>
+        <v>461494</v>
       </c>
       <c r="R3" t="n">
-        <v>6223017.802191476</v>
+        <v>6223066</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,21 +863,450 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>David Göransson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Göransson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104416255</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vångaberget, östsluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461431</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6223018</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Isak Sarac</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Isak Sarac</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104416254</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vångaberget, östsluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461464</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6223114</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107657737</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vånga, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461443</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6223038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bokved</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Göransson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Göransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104416253</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vångaberget, östsluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6223202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnagspår på fnöskticka</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre bokskog i sluttning</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # Fnöskticka</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104416256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107657751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104416255</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104416254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107657737</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,8 +1337,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104416253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104416253</v>
+        <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>44177</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,42 +1223,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vångaberget, östsluttning, Sk</t>
+          <t>Vånga alle, Vånga alle, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461479</v>
+        <v>461445</v>
       </c>
       <c r="R7" t="n">
-        <v>6223202</v>
+        <v>6223185</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,17 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnagspår på fnöskticka</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,43 +1291,155 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre bokskog i sluttning</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fungi, fruit bodies, etc. # Fnöskticka</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136135394</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104416253</v>
+      </c>
+      <c r="B8" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vångaberget, östsluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>461479</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6223202</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnagspår på fnöskticka</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre bokskog i sluttning</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # Fnöskticka</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104416253</t>
         </is>
@@ -1351,6 +1453,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44586-2022 artfynd.xlsx
+++ b/artfynd/A 44586-2022 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>136135394</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
